--- a/Pipe_Matlab_Indici_di_Prestazione_Classica/FOLDER/EXCEL.xlsx
+++ b/Pipe_Matlab_Indici_di_Prestazione_Classica/FOLDER/EXCEL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lachiara\Desktop\Uni_Andrea\Magistrale\Secondo_Anno\Controllo_Avanzato\Pipe_Matlab\FOLDER\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lachiara\Documents\GitHub\ControlloAvanzato\Pipe_Matlab_Indici_di_Prestazione_Classica\FOLDER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2839A6D-5D6E-4EA9-95B5-8D14186EBE24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37895CE6-AA81-4256-99EA-15490F4DA94C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11520" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="68">
   <si>
     <t>Petri net incidence and marking</t>
   </si>
@@ -290,6 +290,21 @@
   </si>
   <si>
     <t>descrizione</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1/2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1/6</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1/5</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1/8</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1/3</t>
   </si>
 </sst>
 </file>
@@ -7975,7 +7990,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="135" spans="1:30" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:30" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
         <v>2</v>
       </c>
@@ -8146,14 +8161,14 @@
       <c r="N139" s="7"/>
     </row>
     <row r="140" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A140">
-        <v>2</v>
-      </c>
-      <c r="B140">
-        <v>6</v>
-      </c>
-      <c r="C140">
-        <v>2</v>
+      <c r="A140" t="s">
+        <v>63</v>
+      </c>
+      <c r="B140" t="s">
+        <v>64</v>
+      </c>
+      <c r="C140" t="s">
+        <v>63</v>
       </c>
       <c r="D140">
         <v>0</v>
@@ -8167,35 +8182,35 @@
       <c r="G140">
         <v>0</v>
       </c>
-      <c r="H140">
-        <v>2</v>
-      </c>
-      <c r="I140">
-        <v>5</v>
-      </c>
-      <c r="J140">
-        <v>2</v>
+      <c r="H140" t="s">
+        <v>63</v>
+      </c>
+      <c r="I140" t="s">
+        <v>65</v>
+      </c>
+      <c r="J140" t="s">
+        <v>63</v>
       </c>
       <c r="K140">
         <v>0</v>
       </c>
-      <c r="L140">
-        <v>2</v>
-      </c>
-      <c r="M140">
-        <v>5</v>
-      </c>
-      <c r="N140" s="7">
-        <v>2</v>
+      <c r="L140" t="s">
+        <v>63</v>
+      </c>
+      <c r="M140" t="s">
+        <v>65</v>
+      </c>
+      <c r="N140" s="7" t="s">
+        <v>63</v>
       </c>
       <c r="O140">
         <v>0</v>
       </c>
-      <c r="P140">
-        <v>8</v>
-      </c>
-      <c r="Q140">
-        <v>3</v>
+      <c r="P140" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q140" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="141" spans="1:30" x14ac:dyDescent="0.3">

--- a/Pipe_Matlab_Indici_di_Prestazione_Classica/FOLDER/EXCEL.xlsx
+++ b/Pipe_Matlab_Indici_di_Prestazione_Classica/FOLDER/EXCEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lachiara\Documents\GitHub\ControlloAvanzato\Pipe_Matlab_Indici_di_Prestazione_Classica\FOLDER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37895CE6-AA81-4256-99EA-15490F4DA94C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8429EC7-828E-43B0-80F1-C11C9A8A8795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="63">
   <si>
     <t>Petri net incidence and marking</t>
   </si>
@@ -291,21 +291,6 @@
   <si>
     <t>descrizione</t>
   </si>
-  <si>
-    <t xml:space="preserve"> 1/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1/6</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1/5</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1/8</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1/3</t>
-  </si>
 </sst>
 </file>
 
@@ -435,7 +420,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -462,6 +447,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -8161,56 +8148,56 @@
       <c r="N139" s="7"/>
     </row>
     <row r="140" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A140" t="s">
-        <v>63</v>
-      </c>
-      <c r="B140" t="s">
-        <v>64</v>
-      </c>
-      <c r="C140" t="s">
-        <v>63</v>
-      </c>
-      <c r="D140">
-        <v>0</v>
-      </c>
-      <c r="E140">
-        <v>0</v>
-      </c>
-      <c r="F140">
-        <v>0</v>
-      </c>
-      <c r="G140">
-        <v>0</v>
-      </c>
-      <c r="H140" t="s">
-        <v>63</v>
-      </c>
-      <c r="I140" t="s">
-        <v>65</v>
-      </c>
-      <c r="J140" t="s">
-        <v>63</v>
-      </c>
-      <c r="K140">
-        <v>0</v>
-      </c>
-      <c r="L140" t="s">
-        <v>63</v>
-      </c>
-      <c r="M140" t="s">
-        <v>65</v>
-      </c>
-      <c r="N140" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="O140">
-        <v>0</v>
-      </c>
-      <c r="P140" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q140" t="s">
-        <v>67</v>
+      <c r="A140" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="B140" s="10">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="C140" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="D140" s="10">
+        <v>0</v>
+      </c>
+      <c r="E140" s="10">
+        <v>0</v>
+      </c>
+      <c r="F140" s="10">
+        <v>0</v>
+      </c>
+      <c r="G140" s="10">
+        <v>0</v>
+      </c>
+      <c r="H140" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="I140" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="J140" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="K140" s="10">
+        <v>0</v>
+      </c>
+      <c r="L140" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="M140" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="N140" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="O140" s="10">
+        <v>0</v>
+      </c>
+      <c r="P140" s="10">
+        <v>0.125</v>
+      </c>
+      <c r="Q140" s="10">
+        <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="141" spans="1:30" x14ac:dyDescent="0.3">

--- a/Pipe_Matlab_Indici_di_Prestazione_Classica/FOLDER/EXCEL.xlsx
+++ b/Pipe_Matlab_Indici_di_Prestazione_Classica/FOLDER/EXCEL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lachiara\Documents\GitHub\ControlloAvanzato\Pipe_Matlab_Indici_di_Prestazione_Classica\FOLDER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8429EC7-828E-43B0-80F1-C11C9A8A8795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{542283BC-315E-4C62-825F-98FF6C9D65E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11520" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -118,13 +118,16 @@
     <t>Ant_Post_Disp_Conforme</t>
   </si>
   <si>
-    <t>Ant_Post_Grezzi_Tagl_Press</t>
+    <t>Ant_Post_Grezzo</t>
+  </si>
+  <si>
+    <t>Ant_Post_Lavorato</t>
   </si>
   <si>
     <t>Ant_Post_Pezzi_Buffer</t>
   </si>
   <si>
-    <t>Ant_Post_Tagliato_Pressato</t>
+    <t>Ant_Post_Tagl_Press</t>
   </si>
   <si>
     <t>Ant_Post_Tagliatrice_Pressa</t>
@@ -154,16 +157,16 @@
     <t>Lat_Dx_Disp_Conforme</t>
   </si>
   <si>
-    <t>Lat_Dx_Grezzi_Tagl_Press</t>
+    <t>Lat_Dx_Grezzo</t>
   </si>
   <si>
-    <t>Lat_Dx_Grezzo</t>
+    <t>Lat_Dx_Lavorato</t>
   </si>
   <si>
     <t>Lat_Dx_Pezzi_Buffer</t>
   </si>
   <si>
-    <t>Lat_Dx_Tagliato_Pressato</t>
+    <t>Lat_Dx_Tagl_Press</t>
   </si>
   <si>
     <t>Lat_Dx_Tagliatrice_Pressa</t>
@@ -178,22 +181,19 @@
     <t>Lat_Sx_Disp_Conforme</t>
   </si>
   <si>
-    <t>Lat_Sx_Greezzi_Tagl_Press</t>
+    <t>Lat_Sx_Grezzo</t>
   </si>
   <si>
-    <t>Lat_Sx_Grezzo</t>
+    <t>Lat_Sx_Lavorato</t>
   </si>
   <si>
     <t>Lat_Sx_Pezzi_Buffer</t>
   </si>
   <si>
-    <t>Lat_Sx_Tagliato_Pressato</t>
+    <t>Lat_Sx_Tagl_Press</t>
   </si>
   <si>
     <t>Lat_Sx_Tagliatrice_Pressa</t>
-  </si>
-  <si>
-    <t>Pezzo_Ant_Post_sul_Nastro</t>
   </si>
   <si>
     <r>
@@ -441,14 +441,14 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="12" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="12" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -738,26 +738,26 @@
       </c>
     </row>
     <row r="3" spans="1:18" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="9"/>
+      <c r="A3" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
     </row>
     <row r="4" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
@@ -981,12 +981,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>22</v>
       </c>
       <c r="B8" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" s="6">
         <v>0</v>
@@ -1001,7 +1001,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="6">
         <v>0</v>
@@ -1037,7 +1037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>23</v>
       </c>
@@ -1045,10 +1045,10 @@
         <v>0</v>
       </c>
       <c r="C9" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="5">
         <v>0</v>
@@ -1101,10 +1101,10 @@
         <v>0</v>
       </c>
       <c r="C10" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="6">
         <v>0</v>
@@ -1154,13 +1154,13 @@
         <v>25</v>
       </c>
       <c r="B11" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" s="5">
         <v>0</v>
       </c>
       <c r="D11" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="5">
         <v>0</v>
@@ -1205,7 +1205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>26</v>
       </c>
@@ -1216,7 +1216,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="6">
         <v>0</v>
@@ -1255,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="Q12" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" s="6">
         <v>0</v>
@@ -1281,7 +1281,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" s="5">
         <v>0</v>
@@ -1311,13 +1311,13 @@
         <v>0</v>
       </c>
       <c r="Q13" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>28</v>
       </c>
@@ -1334,10 +1334,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G14" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="6">
         <v>0</v>
@@ -1373,7 +1373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>29</v>
       </c>
@@ -1390,7 +1390,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G15" s="5">
         <v>0</v>
@@ -1426,7 +1426,7 @@
         <v>0</v>
       </c>
       <c r="R15" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
@@ -1452,7 +1452,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" s="6">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="R16" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>31</v>
       </c>
@@ -1508,7 +1508,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" s="5">
         <v>0</v>
@@ -1520,7 +1520,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" s="5">
         <v>0</v>
@@ -1597,7 +1597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>33</v>
       </c>
@@ -1632,7 +1632,7 @@
         <v>0</v>
       </c>
       <c r="L19" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="5">
         <v>0</v>
@@ -1647,7 +1647,7 @@
         <v>0</v>
       </c>
       <c r="Q19" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" s="5">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" s="6">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>0</v>
       </c>
       <c r="Q20" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" s="6">
         <v>0</v>
@@ -1765,7 +1765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>36</v>
       </c>
@@ -1794,10 +1794,10 @@
         <v>0</v>
       </c>
       <c r="J22" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" s="6">
         <v>0</v>
@@ -1850,10 +1850,10 @@
         <v>0</v>
       </c>
       <c r="J23" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="5">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>38</v>
       </c>
@@ -1903,13 +1903,13 @@
         <v>0</v>
       </c>
       <c r="I24" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="6">
         <v>0</v>
       </c>
       <c r="K24" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="6">
         <v>0</v>
@@ -1933,7 +1933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>39</v>
       </c>
@@ -1965,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="K25" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="5">
         <v>0</v>
@@ -1980,7 +1980,7 @@
         <v>0</v>
       </c>
       <c r="P25" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="5">
         <v>0</v>
@@ -2045,7 +2045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>41</v>
       </c>
@@ -2092,10 +2092,10 @@
         <v>0</v>
       </c>
       <c r="P27" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q27" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" s="5">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M28" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" s="6">
         <v>0</v>
@@ -2151,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="Q28" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" s="6">
         <v>0</v>
@@ -2254,10 +2254,10 @@
         <v>0</v>
       </c>
       <c r="N30" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O30" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P30" s="6">
         <v>0</v>
@@ -2269,7 +2269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>45</v>
       </c>
@@ -2310,10 +2310,10 @@
         <v>0</v>
       </c>
       <c r="N31" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P31" s="5">
         <v>0</v>
@@ -2325,7 +2325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>46</v>
       </c>
@@ -2363,13 +2363,13 @@
         <v>0</v>
       </c>
       <c r="M32" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N32" s="6">
         <v>0</v>
       </c>
       <c r="O32" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P32" s="6">
         <v>0</v>
@@ -2401,7 +2401,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" s="5">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="O33" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P33" s="5">
         <v>0</v>
@@ -2438,26 +2438,26 @@
       </c>
     </row>
     <row r="34" spans="1:18" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="8"/>
-      <c r="I34" s="8"/>
-      <c r="J34" s="8"/>
-      <c r="K34" s="8"/>
-      <c r="L34" s="8"/>
-      <c r="M34" s="8"/>
-      <c r="N34" s="8"/>
-      <c r="O34" s="8"/>
-      <c r="P34" s="8"/>
-      <c r="Q34" s="8"/>
-      <c r="R34" s="8"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="11"/>
+      <c r="O34" s="11"/>
+      <c r="P34" s="11"/>
+      <c r="Q34" s="11"/>
+      <c r="R34" s="11"/>
     </row>
     <row r="35" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A35" s="2"/>
@@ -2681,15 +2681,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>22</v>
       </c>
       <c r="B39" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C39" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39" s="6">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>23</v>
       </c>
@@ -2748,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="D40" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F40" s="5">
         <v>0</v>
@@ -2804,10 +2804,10 @@
         <v>0</v>
       </c>
       <c r="D41" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" s="6">
         <v>0</v>
@@ -2854,10 +2854,10 @@
         <v>25</v>
       </c>
       <c r="B42" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C42" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42" s="5">
         <v>0</v>
@@ -2905,12 +2905,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>26</v>
       </c>
       <c r="B43" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C43" s="6">
         <v>0</v>
@@ -2922,7 +2922,7 @@
         <v>0</v>
       </c>
       <c r="F43" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" s="6">
         <v>0</v>
@@ -2978,13 +2978,13 @@
         <v>0</v>
       </c>
       <c r="F44" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" s="5">
         <v>0</v>
       </c>
       <c r="H44" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44" s="5">
         <v>0</v>
@@ -3017,7 +3017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>28</v>
       </c>
@@ -3040,7 +3040,7 @@
         <v>0</v>
       </c>
       <c r="H45" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I45" s="6">
         <v>0</v>
@@ -3073,7 +3073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>29</v>
       </c>
@@ -3093,10 +3093,10 @@
         <v>0</v>
       </c>
       <c r="G46" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I46" s="5">
         <v>0</v>
@@ -3149,7 +3149,7 @@
         <v>0</v>
       </c>
       <c r="G47" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" s="6">
         <v>0</v>
@@ -3182,10 +3182,10 @@
         <v>0</v>
       </c>
       <c r="R47" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>31</v>
       </c>
@@ -3235,10 +3235,10 @@
         <v>0</v>
       </c>
       <c r="Q48" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R48" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
@@ -3273,7 +3273,7 @@
         <v>0</v>
       </c>
       <c r="K49" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49" s="6">
         <v>0</v>
@@ -3291,13 +3291,13 @@
         <v>0</v>
       </c>
       <c r="Q49" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R49" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>33</v>
       </c>
@@ -3329,10 +3329,10 @@
         <v>0</v>
       </c>
       <c r="K50" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" s="5">
         <v>0</v>
@@ -3382,13 +3382,13 @@
         <v>0</v>
       </c>
       <c r="J51" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" s="6">
         <v>0</v>
       </c>
       <c r="L51" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" s="6">
         <v>0</v>
@@ -3465,7 +3465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>36</v>
       </c>
@@ -3497,10 +3497,10 @@
         <v>0</v>
       </c>
       <c r="K53" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M53" s="6">
         <v>0</v>
@@ -3553,10 +3553,10 @@
         <v>0</v>
       </c>
       <c r="K54" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L54" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" s="5">
         <v>0</v>
@@ -3577,7 +3577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>38</v>
       </c>
@@ -3603,10 +3603,10 @@
         <v>0</v>
       </c>
       <c r="I55" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55" s="6">
         <v>0</v>
@@ -3633,7 +3633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>39</v>
       </c>
@@ -3659,7 +3659,7 @@
         <v>0</v>
       </c>
       <c r="I56" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" s="5">
         <v>0</v>
@@ -3683,7 +3683,7 @@
         <v>0</v>
       </c>
       <c r="Q56" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R56" s="5">
         <v>0</v>
@@ -3733,19 +3733,19 @@
         <v>0</v>
       </c>
       <c r="O57" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P57" s="6">
         <v>0</v>
       </c>
       <c r="Q57" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R57" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>41</v>
       </c>
@@ -3789,10 +3789,10 @@
         <v>0</v>
       </c>
       <c r="O58" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P58" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q58" s="5">
         <v>0</v>
@@ -3842,13 +3842,13 @@
         <v>0</v>
       </c>
       <c r="N59" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O59" s="6">
         <v>0</v>
       </c>
       <c r="P59" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q59" s="6">
         <v>0</v>
@@ -3957,10 +3957,10 @@
         <v>0</v>
       </c>
       <c r="O61" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P61" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q61" s="6">
         <v>0</v>
@@ -3969,7 +3969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
         <v>45</v>
       </c>
@@ -4013,10 +4013,10 @@
         <v>0</v>
       </c>
       <c r="O62" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P62" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q62" s="5">
         <v>0</v>
@@ -4025,7 +4025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
         <v>46</v>
       </c>
@@ -4063,10 +4063,10 @@
         <v>0</v>
       </c>
       <c r="M63" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N63" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O63" s="6">
         <v>0</v>
@@ -4086,7 +4086,7 @@
         <v>47</v>
       </c>
       <c r="B64" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C64" s="5">
         <v>0</v>
@@ -4119,7 +4119,7 @@
         <v>0</v>
       </c>
       <c r="M64" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N64" s="5">
         <v>0</v>
@@ -4138,26 +4138,26 @@
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A65" s="8" t="s">
+      <c r="A65" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="B65" s="8"/>
-      <c r="C65" s="8"/>
-      <c r="D65" s="8"/>
-      <c r="E65" s="8"/>
-      <c r="F65" s="8"/>
-      <c r="G65" s="8"/>
-      <c r="H65" s="8"/>
-      <c r="I65" s="8"/>
-      <c r="J65" s="8"/>
-      <c r="K65" s="8"/>
-      <c r="L65" s="8"/>
-      <c r="M65" s="8"/>
-      <c r="N65" s="8"/>
-      <c r="O65" s="8"/>
-      <c r="P65" s="8"/>
-      <c r="Q65" s="8"/>
-      <c r="R65" s="8"/>
+      <c r="B65" s="11"/>
+      <c r="C65" s="11"/>
+      <c r="D65" s="11"/>
+      <c r="E65" s="11"/>
+      <c r="F65" s="11"/>
+      <c r="G65" s="11"/>
+      <c r="H65" s="11"/>
+      <c r="I65" s="11"/>
+      <c r="J65" s="11"/>
+      <c r="K65" s="11"/>
+      <c r="L65" s="11"/>
+      <c r="M65" s="11"/>
+      <c r="N65" s="11"/>
+      <c r="O65" s="11"/>
+      <c r="P65" s="11"/>
+      <c r="Q65" s="11"/>
+      <c r="R65" s="11"/>
     </row>
     <row r="66" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A66" s="2"/>
@@ -4381,15 +4381,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
         <v>22</v>
       </c>
       <c r="B70" s="6">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="C70" s="6">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D70" s="6">
         <v>0</v>
@@ -4401,7 +4401,7 @@
         <v>0</v>
       </c>
       <c r="G70" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H70" s="6">
         <v>0</v>
@@ -4437,7 +4437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
         <v>23</v>
       </c>
@@ -4445,13 +4445,13 @@
         <v>0</v>
       </c>
       <c r="C71" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D71" s="5">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E71" s="5">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F71" s="5">
         <v>0</v>
@@ -4501,13 +4501,13 @@
         <v>0</v>
       </c>
       <c r="C72" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D72" s="6">
+        <v>1</v>
+      </c>
+      <c r="E72" s="6">
         <v>-1</v>
-      </c>
-      <c r="E72" s="6">
-        <v>0</v>
       </c>
       <c r="F72" s="6">
         <v>0</v>
@@ -4554,13 +4554,13 @@
         <v>25</v>
       </c>
       <c r="B73" s="5">
+        <v>1</v>
+      </c>
+      <c r="C73" s="5">
         <v>-1</v>
       </c>
-      <c r="C73" s="5">
-        <v>0</v>
-      </c>
       <c r="D73" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E73" s="5">
         <v>0</v>
@@ -4605,24 +4605,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
         <v>26</v>
       </c>
       <c r="B74" s="6">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C74" s="6">
         <v>0</v>
       </c>
       <c r="D74" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E74" s="6">
         <v>0</v>
       </c>
       <c r="F74" s="6">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G74" s="6">
         <v>0</v>
@@ -4655,7 +4655,7 @@
         <v>0</v>
       </c>
       <c r="Q74" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R74" s="6">
         <v>0</v>
@@ -4678,13 +4678,13 @@
         <v>0</v>
       </c>
       <c r="F75" s="5">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G75" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H75" s="5">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I75" s="5">
         <v>0</v>
@@ -4711,13 +4711,13 @@
         <v>0</v>
       </c>
       <c r="Q75" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R75" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
         <v>28</v>
       </c>
@@ -4734,13 +4734,13 @@
         <v>0</v>
       </c>
       <c r="F76" s="6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G76" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H76" s="6">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="I76" s="6">
         <v>0</v>
@@ -4773,7 +4773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
         <v>29</v>
       </c>
@@ -4790,13 +4790,13 @@
         <v>0</v>
       </c>
       <c r="F77" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G77" s="5">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H77" s="5">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="I77" s="5">
         <v>0</v>
@@ -4826,7 +4826,7 @@
         <v>0</v>
       </c>
       <c r="R77" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
@@ -4849,10 +4849,10 @@
         <v>0</v>
       </c>
       <c r="G78" s="6">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H78" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I78" s="6">
         <v>0</v>
@@ -4882,10 +4882,10 @@
         <v>0</v>
       </c>
       <c r="R78" s="6">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
         <v>31</v>
       </c>
@@ -4908,7 +4908,7 @@
         <v>0</v>
       </c>
       <c r="H79" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I79" s="5">
         <v>0</v>
@@ -4920,7 +4920,7 @@
         <v>0</v>
       </c>
       <c r="L79" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M79" s="5">
         <v>0</v>
@@ -4935,10 +4935,10 @@
         <v>0</v>
       </c>
       <c r="Q79" s="5">
+        <v>0</v>
+      </c>
+      <c r="R79" s="5">
         <v>-1</v>
-      </c>
-      <c r="R79" s="5">
-        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
@@ -4973,31 +4973,31 @@
         <v>0</v>
       </c>
       <c r="K80" s="6">
+        <v>0</v>
+      </c>
+      <c r="L80" s="6">
+        <v>1</v>
+      </c>
+      <c r="M80" s="6">
+        <v>0</v>
+      </c>
+      <c r="N80" s="6">
+        <v>0</v>
+      </c>
+      <c r="O80" s="6">
+        <v>0</v>
+      </c>
+      <c r="P80" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="6">
         <v>-1</v>
       </c>
-      <c r="L80" s="6">
-        <v>1</v>
-      </c>
-      <c r="M80" s="6">
-        <v>0</v>
-      </c>
-      <c r="N80" s="6">
-        <v>0</v>
-      </c>
-      <c r="O80" s="6">
-        <v>0</v>
-      </c>
-      <c r="P80" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q80" s="6">
-        <v>0</v>
-      </c>
       <c r="R80" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
         <v>33</v>
       </c>
@@ -5029,10 +5029,10 @@
         <v>0</v>
       </c>
       <c r="K81" s="5">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L81" s="5">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="M81" s="5">
         <v>0</v>
@@ -5047,7 +5047,7 @@
         <v>0</v>
       </c>
       <c r="Q81" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R81" s="5">
         <v>0</v>
@@ -5079,17 +5079,17 @@
         <v>0</v>
       </c>
       <c r="I82" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J82" s="6">
+        <v>0</v>
+      </c>
+      <c r="K82" s="6">
+        <v>0</v>
+      </c>
+      <c r="L82" s="6">
         <v>-1</v>
       </c>
-      <c r="K82" s="6">
-        <v>0</v>
-      </c>
-      <c r="L82" s="6">
-        <v>0</v>
-      </c>
       <c r="M82" s="6">
         <v>0</v>
       </c>
@@ -5103,7 +5103,7 @@
         <v>0</v>
       </c>
       <c r="Q82" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R82" s="6">
         <v>0</v>
@@ -5165,7 +5165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
         <v>36</v>
       </c>
@@ -5194,13 +5194,13 @@
         <v>0</v>
       </c>
       <c r="J84" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K84" s="6">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L84" s="6">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M84" s="6">
         <v>0</v>
@@ -5250,14 +5250,14 @@
         <v>0</v>
       </c>
       <c r="J85" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K85" s="5">
+        <v>1</v>
+      </c>
+      <c r="L85" s="5">
         <v>-1</v>
       </c>
-      <c r="L85" s="5">
-        <v>0</v>
-      </c>
       <c r="M85" s="5">
         <v>0</v>
       </c>
@@ -5277,7 +5277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
         <v>38</v>
       </c>
@@ -5303,13 +5303,13 @@
         <v>0</v>
       </c>
       <c r="I86" s="6">
+        <v>1</v>
+      </c>
+      <c r="J86" s="6">
         <v>-1</v>
       </c>
-      <c r="J86" s="6">
-        <v>0</v>
-      </c>
       <c r="K86" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L86" s="6">
         <v>0</v>
@@ -5333,7 +5333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
         <v>39</v>
       </c>
@@ -5359,13 +5359,13 @@
         <v>0</v>
       </c>
       <c r="I87" s="5">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J87" s="5">
         <v>0</v>
       </c>
       <c r="K87" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="5">
         <v>0</v>
@@ -5380,10 +5380,10 @@
         <v>0</v>
       </c>
       <c r="P87" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q87" s="5">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R87" s="5">
         <v>0</v>
@@ -5433,19 +5433,19 @@
         <v>0</v>
       </c>
       <c r="O88" s="6">
+        <v>0</v>
+      </c>
+      <c r="P88" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q88" s="6">
         <v>-1</v>
       </c>
-      <c r="P88" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q88" s="6">
-        <v>0</v>
-      </c>
       <c r="R88" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
         <v>41</v>
       </c>
@@ -5489,13 +5489,13 @@
         <v>0</v>
       </c>
       <c r="O89" s="5">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="P89" s="5">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="Q89" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R89" s="5">
         <v>0</v>
@@ -5539,19 +5539,19 @@
         <v>0</v>
       </c>
       <c r="M90" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N90" s="6">
+        <v>0</v>
+      </c>
+      <c r="O90" s="6">
+        <v>0</v>
+      </c>
+      <c r="P90" s="6">
         <v>-1</v>
       </c>
-      <c r="O90" s="6">
-        <v>0</v>
-      </c>
-      <c r="P90" s="6">
-        <v>0</v>
-      </c>
       <c r="Q90" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R90" s="6">
         <v>0</v>
@@ -5654,13 +5654,13 @@
         <v>0</v>
       </c>
       <c r="N92" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O92" s="6">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="P92" s="6">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q92" s="6">
         <v>0</v>
@@ -5669,7 +5669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
         <v>45</v>
       </c>
@@ -5710,14 +5710,14 @@
         <v>0</v>
       </c>
       <c r="N93" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O93" s="5">
+        <v>1</v>
+      </c>
+      <c r="P93" s="5">
         <v>-1</v>
       </c>
-      <c r="P93" s="5">
-        <v>0</v>
-      </c>
       <c r="Q93" s="5">
         <v>0</v>
       </c>
@@ -5725,7 +5725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
         <v>46</v>
       </c>
@@ -5763,13 +5763,13 @@
         <v>0</v>
       </c>
       <c r="M94" s="6">
+        <v>1</v>
+      </c>
+      <c r="N94" s="6">
         <v>-1</v>
       </c>
-      <c r="N94" s="6">
-        <v>0</v>
-      </c>
       <c r="O94" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P94" s="6">
         <v>0</v>
@@ -5786,46 +5786,46 @@
         <v>47</v>
       </c>
       <c r="B95" s="5">
+        <v>0</v>
+      </c>
+      <c r="C95" s="5">
+        <v>0</v>
+      </c>
+      <c r="D95" s="5">
+        <v>0</v>
+      </c>
+      <c r="E95" s="5">
+        <v>0</v>
+      </c>
+      <c r="F95" s="5">
+        <v>0</v>
+      </c>
+      <c r="G95" s="5">
+        <v>0</v>
+      </c>
+      <c r="H95" s="5">
+        <v>0</v>
+      </c>
+      <c r="I95" s="5">
+        <v>0</v>
+      </c>
+      <c r="J95" s="5">
+        <v>0</v>
+      </c>
+      <c r="K95" s="5">
+        <v>0</v>
+      </c>
+      <c r="L95" s="5">
+        <v>0</v>
+      </c>
+      <c r="M95" s="5">
         <v>-1</v>
       </c>
-      <c r="C95" s="5">
-        <v>0</v>
-      </c>
-      <c r="D95" s="5">
-        <v>0</v>
-      </c>
-      <c r="E95" s="5">
-        <v>0</v>
-      </c>
-      <c r="F95" s="5">
-        <v>0</v>
-      </c>
-      <c r="G95" s="5">
-        <v>1</v>
-      </c>
-      <c r="H95" s="5">
-        <v>0</v>
-      </c>
-      <c r="I95" s="5">
-        <v>0</v>
-      </c>
-      <c r="J95" s="5">
-        <v>0</v>
-      </c>
-      <c r="K95" s="5">
-        <v>0</v>
-      </c>
-      <c r="L95" s="5">
-        <v>0</v>
-      </c>
-      <c r="M95" s="5">
-        <v>0</v>
-      </c>
       <c r="N95" s="5">
         <v>0</v>
       </c>
       <c r="O95" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P95" s="5">
         <v>0</v>
@@ -5838,26 +5838,26 @@
       </c>
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A96" s="8" t="s">
+      <c r="A96" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="B96" s="8"/>
-      <c r="C96" s="8"/>
-      <c r="D96" s="8"/>
-      <c r="E96" s="8"/>
-      <c r="F96" s="8"/>
-      <c r="G96" s="8"/>
-      <c r="H96" s="8"/>
-      <c r="I96" s="8"/>
-      <c r="J96" s="8"/>
-      <c r="K96" s="8"/>
-      <c r="L96" s="8"/>
-      <c r="M96" s="8"/>
-      <c r="N96" s="8"/>
-      <c r="O96" s="8"/>
-      <c r="P96" s="8"/>
-      <c r="Q96" s="8"/>
-      <c r="R96" s="8"/>
+      <c r="B96" s="11"/>
+      <c r="C96" s="11"/>
+      <c r="D96" s="11"/>
+      <c r="E96" s="11"/>
+      <c r="F96" s="11"/>
+      <c r="G96" s="11"/>
+      <c r="H96" s="11"/>
+      <c r="I96" s="11"/>
+      <c r="J96" s="11"/>
+      <c r="K96" s="11"/>
+      <c r="L96" s="11"/>
+      <c r="M96" s="11"/>
+      <c r="N96" s="11"/>
+      <c r="O96" s="11"/>
+      <c r="P96" s="11"/>
+      <c r="Q96" s="11"/>
+      <c r="R96" s="11"/>
     </row>
     <row r="97" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A97" s="2"/>
@@ -6081,7 +6081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
         <v>22</v>
       </c>
@@ -6137,7 +6137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
         <v>23</v>
       </c>
@@ -6305,7 +6305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
         <v>26</v>
       </c>
@@ -6417,7 +6417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
         <v>28</v>
       </c>
@@ -6473,7 +6473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
         <v>29</v>
       </c>
@@ -6585,7 +6585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
         <v>31</v>
       </c>
@@ -6697,7 +6697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
         <v>33</v>
       </c>
@@ -6865,7 +6865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:30" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:30" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
         <v>36</v>
       </c>
@@ -6977,7 +6977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:30" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:30" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
         <v>38</v>
       </c>
@@ -7033,7 +7033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:30" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:30" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
         <v>39</v>
       </c>
@@ -7145,7 +7145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:30" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:30" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
         <v>41</v>
       </c>
@@ -7369,7 +7369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:30" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:30" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A124" s="4" t="s">
         <v>45</v>
       </c>
@@ -7425,7 +7425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:30" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:30" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A125" s="4" t="s">
         <v>46</v>
       </c>
@@ -7538,38 +7538,38 @@
       </c>
     </row>
     <row r="127" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A127" s="8" t="s">
+      <c r="A127" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="B127" s="8"/>
-      <c r="C127" s="8"/>
-      <c r="D127" s="8"/>
-      <c r="E127" s="8"/>
-      <c r="F127" s="8"/>
-      <c r="G127" s="8"/>
-      <c r="H127" s="8"/>
-      <c r="I127" s="8"/>
-      <c r="J127" s="8"/>
-      <c r="K127" s="8"/>
-      <c r="L127" s="8"/>
-      <c r="M127" s="8"/>
-      <c r="N127" s="8"/>
-      <c r="O127" s="8"/>
-      <c r="P127" s="8"/>
-      <c r="Q127" s="8"/>
-      <c r="R127" s="8"/>
-      <c r="S127" s="8"/>
-      <c r="T127" s="8"/>
-      <c r="U127" s="8"/>
-      <c r="V127" s="8"/>
-      <c r="W127" s="8"/>
-      <c r="X127" s="8"/>
-      <c r="Y127" s="8"/>
-      <c r="Z127" s="8"/>
-      <c r="AA127" s="8"/>
-      <c r="AB127" s="8"/>
-      <c r="AC127" s="8"/>
-      <c r="AD127" s="8"/>
+      <c r="B127" s="11"/>
+      <c r="C127" s="11"/>
+      <c r="D127" s="11"/>
+      <c r="E127" s="11"/>
+      <c r="F127" s="11"/>
+      <c r="G127" s="11"/>
+      <c r="H127" s="11"/>
+      <c r="I127" s="11"/>
+      <c r="J127" s="11"/>
+      <c r="K127" s="11"/>
+      <c r="L127" s="11"/>
+      <c r="M127" s="11"/>
+      <c r="N127" s="11"/>
+      <c r="O127" s="11"/>
+      <c r="P127" s="11"/>
+      <c r="Q127" s="11"/>
+      <c r="R127" s="11"/>
+      <c r="S127" s="11"/>
+      <c r="T127" s="11"/>
+      <c r="U127" s="11"/>
+      <c r="V127" s="11"/>
+      <c r="W127" s="11"/>
+      <c r="X127" s="11"/>
+      <c r="Y127" s="11"/>
+      <c r="Z127" s="11"/>
+      <c r="AA127" s="11"/>
+      <c r="AB127" s="11"/>
+      <c r="AC127" s="11"/>
+      <c r="AD127" s="11"/>
     </row>
     <row r="128" spans="1:30" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A128" s="2"/>
@@ -7684,20 +7684,20 @@
         <v>0</v>
       </c>
       <c r="H129" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I129" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J129" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K129" s="5">
+        <v>0</v>
+      </c>
+      <c r="L129" s="5">
         <v>9</v>
       </c>
-      <c r="L129" s="5">
-        <v>0</v>
-      </c>
       <c r="M129" s="5">
         <v>0</v>
       </c>
@@ -7705,13 +7705,13 @@
         <v>0</v>
       </c>
       <c r="O129" s="5">
+        <v>0</v>
+      </c>
+      <c r="P129" s="5">
         <v>2</v>
       </c>
-      <c r="P129" s="5">
-        <v>1</v>
-      </c>
       <c r="Q129" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R129" s="5">
         <v>0</v>
@@ -7723,19 +7723,19 @@
         <v>0</v>
       </c>
       <c r="U129" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V129" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W129" s="5">
+        <v>0</v>
+      </c>
+      <c r="X129" s="5">
         <v>2</v>
       </c>
-      <c r="X129" s="5">
-        <v>1</v>
-      </c>
       <c r="Y129" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z129" s="5">
         <v>0</v>
@@ -7747,10 +7747,10 @@
         <v>0</v>
       </c>
       <c r="AC129" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD129" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:30" x14ac:dyDescent="0.3">
@@ -7776,20 +7776,20 @@
         <v>0</v>
       </c>
       <c r="H130" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I130" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J130" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K130" s="6">
+        <v>0</v>
+      </c>
+      <c r="L130" s="6">
         <v>9</v>
       </c>
-      <c r="L130" s="6">
-        <v>0</v>
-      </c>
       <c r="M130" s="6">
         <v>0</v>
       </c>
@@ -7797,13 +7797,13 @@
         <v>0</v>
       </c>
       <c r="O130" s="6">
+        <v>0</v>
+      </c>
+      <c r="P130" s="6">
         <v>2</v>
       </c>
-      <c r="P130" s="6">
-        <v>1</v>
-      </c>
       <c r="Q130" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R130" s="6">
         <v>0</v>
@@ -7815,19 +7815,19 @@
         <v>0</v>
       </c>
       <c r="U130" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V130" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W130" s="6">
+        <v>0</v>
+      </c>
+      <c r="X130" s="6">
         <v>2</v>
       </c>
-      <c r="X130" s="6">
-        <v>1</v>
-      </c>
       <c r="Y130" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z130" s="6">
         <v>0</v>
@@ -7839,32 +7839,32 @@
         <v>0</v>
       </c>
       <c r="AC130" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD130" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A131" s="8" t="s">
+      <c r="A131" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="B131" s="8"/>
-      <c r="C131" s="8"/>
-      <c r="D131" s="8"/>
-      <c r="E131" s="8"/>
-      <c r="F131" s="8"/>
-      <c r="G131" s="8"/>
-      <c r="H131" s="8"/>
-      <c r="I131" s="8"/>
-      <c r="J131" s="8"/>
-      <c r="K131" s="8"/>
-      <c r="L131" s="8"/>
-      <c r="M131" s="8"/>
-      <c r="N131" s="8"/>
-      <c r="O131" s="8"/>
-      <c r="P131" s="8"/>
-      <c r="Q131" s="8"/>
+      <c r="B131" s="11"/>
+      <c r="C131" s="11"/>
+      <c r="D131" s="11"/>
+      <c r="E131" s="11"/>
+      <c r="F131" s="11"/>
+      <c r="G131" s="11"/>
+      <c r="H131" s="11"/>
+      <c r="I131" s="11"/>
+      <c r="J131" s="11"/>
+      <c r="K131" s="11"/>
+      <c r="L131" s="11"/>
+      <c r="M131" s="11"/>
+      <c r="N131" s="11"/>
+      <c r="O131" s="11"/>
+      <c r="P131" s="11"/>
+      <c r="Q131" s="11"/>
     </row>
     <row r="132" spans="1:30" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
@@ -7939,7 +7939,7 @@
         <v>55</v>
       </c>
       <c r="G133" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H133" s="5" t="s">
         <v>55</v>
@@ -7977,7 +7977,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="135" spans="1:30" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:30" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
         <v>2</v>
       </c>
@@ -8148,55 +8148,55 @@
       <c r="N139" s="7"/>
     </row>
     <row r="140" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A140" s="10">
+      <c r="A140" s="8">
         <v>0.5</v>
       </c>
-      <c r="B140" s="10">
+      <c r="B140" s="8">
         <v>0.16666666666666666</v>
       </c>
-      <c r="C140" s="10">
+      <c r="C140" s="8">
         <v>0.5</v>
       </c>
-      <c r="D140" s="10">
-        <v>0</v>
-      </c>
-      <c r="E140" s="10">
-        <v>0</v>
-      </c>
-      <c r="F140" s="10">
-        <v>0</v>
-      </c>
-      <c r="G140" s="10">
-        <v>0</v>
-      </c>
-      <c r="H140" s="10">
+      <c r="D140" s="8">
+        <v>0</v>
+      </c>
+      <c r="E140" s="8">
+        <v>0</v>
+      </c>
+      <c r="F140" s="8">
+        <v>0</v>
+      </c>
+      <c r="G140" s="8">
+        <v>0</v>
+      </c>
+      <c r="H140" s="8">
         <v>0.5</v>
       </c>
-      <c r="I140" s="10">
+      <c r="I140" s="8">
         <v>0.2</v>
       </c>
-      <c r="J140" s="10">
+      <c r="J140" s="8">
         <v>0.5</v>
       </c>
-      <c r="K140" s="10">
-        <v>0</v>
-      </c>
-      <c r="L140" s="10">
+      <c r="K140" s="8">
+        <v>0</v>
+      </c>
+      <c r="L140" s="8">
         <v>0.5</v>
       </c>
-      <c r="M140" s="10">
+      <c r="M140" s="8">
         <v>0.2</v>
       </c>
-      <c r="N140" s="11">
+      <c r="N140" s="9">
         <v>0.5</v>
       </c>
-      <c r="O140" s="10">
-        <v>0</v>
-      </c>
-      <c r="P140" s="10">
+      <c r="O140" s="8">
+        <v>0</v>
+      </c>
+      <c r="P140" s="8">
         <v>0.125</v>
       </c>
-      <c r="Q140" s="10">
+      <c r="Q140" s="8">
         <v>0.33333333333333331</v>
       </c>
     </row>

--- a/Pipe_Matlab_Indici_di_Prestazione_Classica/FOLDER/EXCEL.xlsx
+++ b/Pipe_Matlab_Indici_di_Prestazione_Classica/FOLDER/EXCEL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lachiara\Documents\GitHub\ControlloAvanzato\Pipe_Matlab_Indici_di_Prestazione_Classica\FOLDER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{542283BC-315E-4C62-825F-98FF6C9D65E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B859AD40-04FE-4B55-BCAB-1D63FDFDDB15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11520" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -443,10 +443,10 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="12" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="12" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -738,26 +738,26 @@
       </c>
     </row>
     <row r="3" spans="1:18" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
-      <c r="O3" s="10"/>
-      <c r="P3" s="10"/>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="10"/>
+      <c r="A3" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="11"/>
+      <c r="Q3" s="11"/>
+      <c r="R3" s="11"/>
     </row>
     <row r="4" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
@@ -2438,26 +2438,26 @@
       </c>
     </row>
     <row r="34" spans="1:18" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="11" t="s">
+      <c r="A34" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="11"/>
-      <c r="J34" s="11"/>
-      <c r="K34" s="11"/>
-      <c r="L34" s="11"/>
-      <c r="M34" s="11"/>
-      <c r="N34" s="11"/>
-      <c r="O34" s="11"/>
-      <c r="P34" s="11"/>
-      <c r="Q34" s="11"/>
-      <c r="R34" s="11"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="10"/>
+      <c r="J34" s="10"/>
+      <c r="K34" s="10"/>
+      <c r="L34" s="10"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="10"/>
+      <c r="O34" s="10"/>
+      <c r="P34" s="10"/>
+      <c r="Q34" s="10"/>
+      <c r="R34" s="10"/>
     </row>
     <row r="35" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A35" s="2"/>
@@ -4138,26 +4138,26 @@
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A65" s="11" t="s">
+      <c r="A65" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B65" s="11"/>
-      <c r="C65" s="11"/>
-      <c r="D65" s="11"/>
-      <c r="E65" s="11"/>
-      <c r="F65" s="11"/>
-      <c r="G65" s="11"/>
-      <c r="H65" s="11"/>
-      <c r="I65" s="11"/>
-      <c r="J65" s="11"/>
-      <c r="K65" s="11"/>
-      <c r="L65" s="11"/>
-      <c r="M65" s="11"/>
-      <c r="N65" s="11"/>
-      <c r="O65" s="11"/>
-      <c r="P65" s="11"/>
-      <c r="Q65" s="11"/>
-      <c r="R65" s="11"/>
+      <c r="B65" s="10"/>
+      <c r="C65" s="10"/>
+      <c r="D65" s="10"/>
+      <c r="E65" s="10"/>
+      <c r="F65" s="10"/>
+      <c r="G65" s="10"/>
+      <c r="H65" s="10"/>
+      <c r="I65" s="10"/>
+      <c r="J65" s="10"/>
+      <c r="K65" s="10"/>
+      <c r="L65" s="10"/>
+      <c r="M65" s="10"/>
+      <c r="N65" s="10"/>
+      <c r="O65" s="10"/>
+      <c r="P65" s="10"/>
+      <c r="Q65" s="10"/>
+      <c r="R65" s="10"/>
     </row>
     <row r="66" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A66" s="2"/>
@@ -5838,26 +5838,26 @@
       </c>
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A96" s="11" t="s">
+      <c r="A96" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B96" s="11"/>
-      <c r="C96" s="11"/>
-      <c r="D96" s="11"/>
-      <c r="E96" s="11"/>
-      <c r="F96" s="11"/>
-      <c r="G96" s="11"/>
-      <c r="H96" s="11"/>
-      <c r="I96" s="11"/>
-      <c r="J96" s="11"/>
-      <c r="K96" s="11"/>
-      <c r="L96" s="11"/>
-      <c r="M96" s="11"/>
-      <c r="N96" s="11"/>
-      <c r="O96" s="11"/>
-      <c r="P96" s="11"/>
-      <c r="Q96" s="11"/>
-      <c r="R96" s="11"/>
+      <c r="B96" s="10"/>
+      <c r="C96" s="10"/>
+      <c r="D96" s="10"/>
+      <c r="E96" s="10"/>
+      <c r="F96" s="10"/>
+      <c r="G96" s="10"/>
+      <c r="H96" s="10"/>
+      <c r="I96" s="10"/>
+      <c r="J96" s="10"/>
+      <c r="K96" s="10"/>
+      <c r="L96" s="10"/>
+      <c r="M96" s="10"/>
+      <c r="N96" s="10"/>
+      <c r="O96" s="10"/>
+      <c r="P96" s="10"/>
+      <c r="Q96" s="10"/>
+      <c r="R96" s="10"/>
     </row>
     <row r="97" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A97" s="2"/>
@@ -7538,38 +7538,38 @@
       </c>
     </row>
     <row r="127" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A127" s="11" t="s">
+      <c r="A127" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="B127" s="11"/>
-      <c r="C127" s="11"/>
-      <c r="D127" s="11"/>
-      <c r="E127" s="11"/>
-      <c r="F127" s="11"/>
-      <c r="G127" s="11"/>
-      <c r="H127" s="11"/>
-      <c r="I127" s="11"/>
-      <c r="J127" s="11"/>
-      <c r="K127" s="11"/>
-      <c r="L127" s="11"/>
-      <c r="M127" s="11"/>
-      <c r="N127" s="11"/>
-      <c r="O127" s="11"/>
-      <c r="P127" s="11"/>
-      <c r="Q127" s="11"/>
-      <c r="R127" s="11"/>
-      <c r="S127" s="11"/>
-      <c r="T127" s="11"/>
-      <c r="U127" s="11"/>
-      <c r="V127" s="11"/>
-      <c r="W127" s="11"/>
-      <c r="X127" s="11"/>
-      <c r="Y127" s="11"/>
-      <c r="Z127" s="11"/>
-      <c r="AA127" s="11"/>
-      <c r="AB127" s="11"/>
-      <c r="AC127" s="11"/>
-      <c r="AD127" s="11"/>
+      <c r="B127" s="10"/>
+      <c r="C127" s="10"/>
+      <c r="D127" s="10"/>
+      <c r="E127" s="10"/>
+      <c r="F127" s="10"/>
+      <c r="G127" s="10"/>
+      <c r="H127" s="10"/>
+      <c r="I127" s="10"/>
+      <c r="J127" s="10"/>
+      <c r="K127" s="10"/>
+      <c r="L127" s="10"/>
+      <c r="M127" s="10"/>
+      <c r="N127" s="10"/>
+      <c r="O127" s="10"/>
+      <c r="P127" s="10"/>
+      <c r="Q127" s="10"/>
+      <c r="R127" s="10"/>
+      <c r="S127" s="10"/>
+      <c r="T127" s="10"/>
+      <c r="U127" s="10"/>
+      <c r="V127" s="10"/>
+      <c r="W127" s="10"/>
+      <c r="X127" s="10"/>
+      <c r="Y127" s="10"/>
+      <c r="Z127" s="10"/>
+      <c r="AA127" s="10"/>
+      <c r="AB127" s="10"/>
+      <c r="AC127" s="10"/>
+      <c r="AD127" s="10"/>
     </row>
     <row r="128" spans="1:30" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A128" s="2"/>
@@ -7693,7 +7693,7 @@
         <v>0</v>
       </c>
       <c r="K129" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L129" s="5">
         <v>9</v>
@@ -7785,7 +7785,7 @@
         <v>0</v>
       </c>
       <c r="K130" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L130" s="6">
         <v>9</v>
@@ -7846,25 +7846,25 @@
       </c>
     </row>
     <row r="131" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A131" s="11" t="s">
+      <c r="A131" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B131" s="11"/>
-      <c r="C131" s="11"/>
-      <c r="D131" s="11"/>
-      <c r="E131" s="11"/>
-      <c r="F131" s="11"/>
-      <c r="G131" s="11"/>
-      <c r="H131" s="11"/>
-      <c r="I131" s="11"/>
-      <c r="J131" s="11"/>
-      <c r="K131" s="11"/>
-      <c r="L131" s="11"/>
-      <c r="M131" s="11"/>
-      <c r="N131" s="11"/>
-      <c r="O131" s="11"/>
-      <c r="P131" s="11"/>
-      <c r="Q131" s="11"/>
+      <c r="B131" s="10"/>
+      <c r="C131" s="10"/>
+      <c r="D131" s="10"/>
+      <c r="E131" s="10"/>
+      <c r="F131" s="10"/>
+      <c r="G131" s="10"/>
+      <c r="H131" s="10"/>
+      <c r="I131" s="10"/>
+      <c r="J131" s="10"/>
+      <c r="K131" s="10"/>
+      <c r="L131" s="10"/>
+      <c r="M131" s="10"/>
+      <c r="N131" s="10"/>
+      <c r="O131" s="10"/>
+      <c r="P131" s="10"/>
+      <c r="Q131" s="10"/>
     </row>
     <row r="132" spans="1:30" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
@@ -7939,7 +7939,7 @@
         <v>55</v>
       </c>
       <c r="G133" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H133" s="5" t="s">
         <v>55</v>
